--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,86 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -745,23 +745,26 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3">
         <v>200</v>
       </c>
       <c r="F8" s="3">
+        <v>200</v>
+      </c>
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -777,8 +780,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -804,13 +807,16 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -818,8 +824,8 @@
       <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="G9" s="3">
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -839,20 +845,20 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3">
         <v>1900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
+      <c r="R9" s="3">
+        <v>0</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
@@ -863,23 +869,26 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
       </c>
       <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,20 +907,20 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3">
         <v>-1900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-100</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
+      <c r="R10" s="3">
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
@@ -922,8 +931,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,50 +957,51 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E12" s="3">
         <v>15000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27600</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1017,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,26 +1079,29 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,12 +1120,12 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1122,8 +1141,11 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1203,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,55 +1226,56 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E17" s="3">
         <v>27400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
@@ -1260,23 +1286,26 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29200</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1292,23 +1321,23 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-32200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-36700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
+      <c r="R18" s="3">
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
@@ -1319,8 +1348,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,23 +1374,24 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5600</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1374,23 +1407,23 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1401,23 +1434,26 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-23600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-24500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22800</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1433,18 +1469,18 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-35500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-35700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1496,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1474,8 +1513,8 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1483,11 +1522,11 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1496,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1510,8 +1549,8 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1519,55 +1558,58 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-33100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
@@ -1578,8 +1620,11 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1637,8 +1682,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,55 +1744,58 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-36600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
@@ -1755,55 +1806,58 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-36600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
@@ -1814,8 +1868,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1930,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1992,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2054,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,23 +2116,26 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5600</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,23 +2151,23 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2109,55 +2178,58 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-36600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
@@ -2168,8 +2240,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,55 +2302,58 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-36600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
@@ -2286,61 +2364,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2350,8 +2431,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2457,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,55 +2481,56 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E41" s="3">
         <v>93800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>87900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>81700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>81300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>62100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>521900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>37900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
@@ -2455,49 +2541,52 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E42" s="3">
         <v>180800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>209300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>240400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>267000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>293800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>319400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>399800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>435500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>438100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -2505,8 +2594,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2514,23 +2603,26 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2638,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2573,23 +2665,26 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1700</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,8 +2700,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2632,56 +2727,59 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E45" s="3">
         <v>7400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,56 +2789,59 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>266300</v>
+      </c>
+      <c r="E46" s="3">
         <v>284800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>306800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>330000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>358200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>378900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>405100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>439800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>477200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>505200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>524100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +2851,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2782,11 +2886,11 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
-        <v>115000</v>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>115000</v>
@@ -2794,8 +2898,8 @@
       <c r="P47" s="3">
         <v>115000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>115000</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2809,58 +2913,61 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E48" s="3">
         <v>32000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3">
         <v>2000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2868,25 +2975,28 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>500</v>
+      </c>
+      <c r="E49" s="3">
         <v>600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>900</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>9500</v>
@@ -2897,8 +3007,8 @@
       <c r="K49" s="3">
         <v>9500</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>9500</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2906,17 +3016,17 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2927,8 +3037,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3099,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,8 +3161,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3075,28 +3194,28 @@
         <v>700</v>
       </c>
       <c r="L52" s="3">
+        <v>700</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3104,8 +3223,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,56 +3285,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E54" s="3">
         <v>318100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>341200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>365000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>391500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>418000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>443300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>476100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>503200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>509500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>527000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>115800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>116300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3347,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3373,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,52 +3397,53 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3327,8 +3457,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3368,14 +3501,14 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3386,56 +3519,59 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E59" s="3">
         <v>9000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
       <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,55 +3581,58 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E60" s="3">
         <v>11000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
-      </c>
-      <c r="P60" s="3">
-        <v>100</v>
       </c>
       <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
+      <c r="R60" s="3">
+        <v>100</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
@@ -3504,8 +3643,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3563,8 +3705,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3572,44 +3717,44 @@
         <v>15000</v>
       </c>
       <c r="E62" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F62" s="3">
         <v>15700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3767,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3829,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3891,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,56 +3953,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E66" s="3">
         <v>26000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4015,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4041,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4101,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4163,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4038,11 +4205,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>195800</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4058,8 +4225,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,55 +4287,58 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-495600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-473600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-448900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-423300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-399700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-366500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-334800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-302400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-267200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-237800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-219700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-172200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -4176,8 +4349,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4411,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4473,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,55 +4535,58 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>271600</v>
+      </c>
+      <c r="E76" s="3">
         <v>292100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>315300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>339000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>358700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>387500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>413500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>441900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>477000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>493900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>503900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>97100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-159700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>112200</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
@@ -4412,8 +4597,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,61 +4659,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4535,55 +4726,58 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-36600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
@@ -4594,8 +4788,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,58 +4814,59 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>800</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
       </c>
       <c r="H83" s="3">
+        <v>800</v>
+      </c>
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
       </c>
       <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="P83" s="3">
         <v>900</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4676,8 +4874,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4936,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4998,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5060,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5122,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,50 +5184,53 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-29400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5030,8 +5246,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,49 +5272,50 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-3500</v>
       </c>
       <c r="G91" s="3">
         <v>-3500</v>
       </c>
       <c r="H91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-500</v>
       </c>
       <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>-500</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5103,8 +5323,8 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5112,8 +5332,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5394,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,49 +5456,52 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E94" s="3">
         <v>27100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>29200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>26000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>25500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>17200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>72800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>21700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-439900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-500</v>
       </c>
       <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>-500</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5280,8 +5509,8 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -5289,8 +5518,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5544,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5604,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5666,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5728,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,50 +5790,53 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>515200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>116300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5607,8 +5852,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5666,50 +5914,53 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E102" s="3">
         <v>5900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>46300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-459800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>485500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5723,6 +5974,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,89 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -748,26 +749,29 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>200</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
       </c>
       <c r="G8" s="3">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,8 +787,8 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -810,8 +814,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -819,7 +826,7 @@
         <v>200</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -827,8 +834,8 @@
       <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>100</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -848,20 +855,20 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
         <v>1900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
+      <c r="S9" s="3">
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
@@ -872,26 +879,29 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,20 +920,20 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3">
         <v>-1900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
+      <c r="S10" s="3">
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
@@ -934,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,53 +971,54 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E12" s="3">
         <v>16100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27600</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1082,29 +1099,32 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1123,12 +1143,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,8 +1164,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1206,8 +1229,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,58 +1253,59 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E17" s="3">
         <v>28300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1289,26 +1316,29 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-27200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-29200</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1324,23 +1354,23 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-32200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
+      <c r="S18" s="3">
+        <v>0</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
@@ -1351,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,26 +1408,27 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E20" s="3">
         <v>5800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5600</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1410,23 +1444,23 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>-3500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1437,26 +1471,29 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-24500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22800</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1472,18 +1509,18 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-35500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,8 +1536,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1516,8 +1556,8 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1525,11 +1565,11 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1538,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1552,8 +1592,8 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1561,58 +1601,61 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-33100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-29400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1623,8 +1666,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1685,8 +1731,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1747,58 +1796,61 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-35200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-29400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1809,58 +1861,61 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-29400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1871,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1995,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2057,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2119,26 +2186,29 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5600</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2154,23 +2224,23 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>3500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2181,58 +2251,61 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-32400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2243,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,58 +2381,61 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-32400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2367,64 +2446,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,58 +2568,59 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E41" s="3">
         <v>133900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>93800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>87900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>81700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>84300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>78300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>81300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>62100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>521900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2544,52 +2631,55 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>182300</v>
+      </c>
+      <c r="E42" s="3">
         <v>123900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>180800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>209300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>240400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>267000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>293800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>319400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>399800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>435500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>438100</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -2597,8 +2687,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2606,26 +2696,29 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2641,8 +2734,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2668,26 +2761,29 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E44" s="3">
         <v>3900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1700</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2703,8 +2799,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2730,59 +2826,62 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,59 +2891,62 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>244400</v>
+      </c>
+      <c r="E46" s="3">
         <v>266300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>284800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>306800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>330000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>358200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>378900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>405100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>439800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>477200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>505200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>524100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2854,8 +2956,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2889,11 +2994,11 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>115000</v>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>115000</v>
@@ -2901,8 +3006,8 @@
       <c r="Q47" s="3">
         <v>115000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>115000</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2916,61 +3021,64 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E48" s="3">
         <v>30700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3">
         <v>2000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2978,8 +3086,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2987,19 +3098,19 @@
         <v>500</v>
       </c>
       <c r="E49" s="3">
+        <v>500</v>
+      </c>
+      <c r="F49" s="3">
         <v>600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>900</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>9500</v>
@@ -3010,8 +3121,8 @@
       <c r="L49" s="3">
         <v>9500</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>9500</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -3019,17 +3130,17 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3040,8 +3151,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3102,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3164,8 +3281,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3197,28 +3317,28 @@
         <v>700</v>
       </c>
       <c r="M52" s="3">
+        <v>700</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3226,8 +3346,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3288,59 +3411,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>275600</v>
+      </c>
+      <c r="E54" s="3">
         <v>298300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>318100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>341200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>365000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>391500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>418000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>443300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>476100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>503200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>509500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>527000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>115800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>116300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,55 +3528,56 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3460,8 +3591,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3504,14 +3638,14 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3522,59 +3656,62 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E59" s="3">
         <v>9800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4800</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,58 +3721,61 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>100</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>100</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3646,8 +3786,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3708,56 +3851,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15000</v>
+        <v>13800</v>
       </c>
       <c r="E62" s="3">
         <v>15000</v>
       </c>
       <c r="F62" s="3">
+        <v>15000</v>
+      </c>
+      <c r="G62" s="3">
         <v>15700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3770,8 +3916,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3832,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3894,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3956,59 +4111,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E66" s="3">
         <v>26600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4018,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4104,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,11 +4376,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>195800</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4228,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4290,58 +4461,61 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-515100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-495600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-473600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-448900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-423300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-399700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-366500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-334800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-302400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-267200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-237800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-219700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-172200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4352,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4414,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4476,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4538,58 +4721,61 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>253800</v>
+      </c>
+      <c r="E76" s="3">
         <v>271600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>292100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>315300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>339000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>358700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>387500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>413500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>441900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>477000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>493900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>503900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>112200</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4600,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4662,64 +4851,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4729,58 +4921,61 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-32400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4791,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,8 +5013,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4824,52 +5023,52 @@
         <v>1100</v>
       </c>
       <c r="E83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
       </c>
       <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
       </c>
       <c r="N83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4877,8 +5076,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4939,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5001,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5063,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5125,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5187,53 +5401,56 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,52 +5493,53 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3500</v>
       </c>
       <c r="H91" s="3">
         <v>-3500</v>
       </c>
       <c r="I91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-500</v>
       </c>
       <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>-500</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5326,8 +5547,8 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5335,8 +5556,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5397,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5459,52 +5686,55 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="E94" s="3">
         <v>61100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>27100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>29200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>26000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>17200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>72800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>21700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-439900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-700</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-500</v>
       </c>
       <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>-500</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5512,8 +5742,8 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5521,8 +5751,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5607,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5669,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5731,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5793,8 +6036,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5802,44 +6048,44 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>515200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>116300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,31 +6101,34 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5917,53 +6166,56 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="E102" s="3">
         <v>40000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>46300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-459800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>485500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,29 +753,32 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>200</v>
       </c>
       <c r="G8" s="3">
         <v>200</v>
       </c>
       <c r="H8" s="3">
+        <v>200</v>
+      </c>
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -790,8 +794,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -817,19 +821,22 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E9" s="3">
         <v>200</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G9" s="3">
         <v>100</v>
@@ -837,8 +844,8 @@
       <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="I9" s="3">
+        <v>100</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -858,20 +865,20 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
+      <c r="T9" s="3">
+        <v>0</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
@@ -882,8 +889,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,20 +901,20 @@
         <v>300</v>
       </c>
       <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,20 +933,20 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-100</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
+      <c r="T10" s="3">
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,56 +985,57 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E12" s="3">
         <v>12000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27600</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,32 +1119,35 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1146,12 +1166,12 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1167,8 +1187,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,61 +1280,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E17" s="3">
         <v>23800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1319,29 +1346,32 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-23300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-27900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-26900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29200</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1357,23 +1387,23 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-32200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-36700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
+      <c r="T18" s="3">
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,29 +1442,30 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>3800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5600</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1447,23 +1481,23 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-3500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1474,29 +1508,32 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-24500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-22800</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1512,18 +1549,18 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-35500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-35700</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1576,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1559,8 +1599,8 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1568,11 +1608,11 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1581,13 +1621,13 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1595,8 +1635,8 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1604,61 +1644,64 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-33100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-35200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-29400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-35700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1669,8 +1712,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,61 +1848,64 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-23600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-32400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-35200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-29400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-35700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-36600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1864,61 +1916,64 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-32400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-35200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-29400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-35700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,29 +2256,32 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5600</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,23 +2297,23 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>3500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2254,61 +2324,64 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-32400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-35200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-29400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-35700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-36600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,61 +2460,64 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-32400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-35200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-29400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-35700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-36600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2449,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,61 +2655,62 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E41" s="3">
         <v>53200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>133900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>93800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>81700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>84300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>78300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>81300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>35800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>62100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>521900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>37900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2634,55 +2721,58 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E42" s="3">
         <v>182300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>123900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>180800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>209300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>240400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>267000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>293800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>319400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>399800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>435500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>438100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
@@ -2690,8 +2780,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2699,29 +2789,32 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2737,8 +2830,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2764,8 +2857,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2773,20 +2869,20 @@
         <v>4900</v>
       </c>
       <c r="E44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F44" s="3">
         <v>3900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1700</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2802,8 +2898,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2829,62 +2925,65 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,62 +2993,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>226500</v>
+      </c>
+      <c r="E46" s="3">
         <v>244400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>266300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>284800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>306800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>330000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>358200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>378900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>405100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>439800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>477200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>505200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>524100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2997,11 +3102,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>115000</v>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>115000</v>
@@ -3009,8 +3114,8 @@
       <c r="R47" s="3">
         <v>115000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>115000</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3024,64 +3129,67 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E48" s="3">
         <v>30000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3">
         <v>2000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3089,31 +3197,34 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>500</v>
       </c>
       <c r="F49" s="3">
+        <v>500</v>
+      </c>
+      <c r="G49" s="3">
         <v>600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>900</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>9500</v>
@@ -3124,8 +3235,8 @@
       <c r="M49" s="3">
         <v>9500</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>9500</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -3133,17 +3244,17 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,8 +3401,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3320,28 +3440,28 @@
         <v>700</v>
       </c>
       <c r="N52" s="3">
+        <v>700</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
         <v>700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,62 +3537,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>256700</v>
+      </c>
+      <c r="E54" s="3">
         <v>275600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>298300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>318100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>341200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>365000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>391500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>418000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>443300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>476100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>503200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>509500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>527000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>115800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>116300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,58 +3659,59 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3594,8 +3725,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3641,14 +3775,14 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3659,62 +3793,65 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E59" s="3">
         <v>6800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>1400</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
       <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,61 +3861,64 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2800</v>
-      </c>
-      <c r="R60" s="3">
-        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>100</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
@@ -3789,8 +3929,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3854,59 +3997,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E62" s="3">
         <v>13800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>15000</v>
       </c>
       <c r="F62" s="3">
         <v>15000</v>
       </c>
       <c r="G62" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H62" s="3">
         <v>15700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,62 +4269,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E66" s="3">
         <v>21800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4379,11 +4547,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>195800</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,61 +4635,64 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-538200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-515100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-495600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-473600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-448900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-423300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-399700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-366500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-334800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-302400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-267200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-237800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-219700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-172200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,61 +4907,64 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>233300</v>
+      </c>
+      <c r="E76" s="3">
         <v>253800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>271600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>292100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>315300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>339000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>358700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>387500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>413500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>441900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>477000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>493900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>503900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-159700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>112200</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,61 +5116,64 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-32400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-35200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-29400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-35700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-36600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,64 +5212,65 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
       </c>
       <c r="F83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>800</v>
       </c>
       <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,56 +5618,59 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-23200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,8 +5714,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5503,46 +5724,46 @@
         <v>-1100</v>
       </c>
       <c r="E91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-3500</v>
       </c>
       <c r="I91" s="3">
         <v>-3500</v>
       </c>
       <c r="J91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-500</v>
       </c>
       <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>-500</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5550,8 +5771,8 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,55 +5916,58 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>61100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>27100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>29200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>26000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>25500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>17200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>72800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>21700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-439900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-500</v>
       </c>
       <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>-500</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5745,8 +5975,8 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,56 +6282,59 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>515200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>116300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,16 +6350,19 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -6130,8 +6379,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6169,56 +6418,59 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-80700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>40000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>46300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-459800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>485500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,32 +757,35 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>200</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
       <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -797,8 +801,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -824,22 +828,25 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>300</v>
-      </c>
-      <c r="E9" s="3">
-        <v>200</v>
       </c>
       <c r="F9" s="3">
         <v>200</v>
       </c>
       <c r="G9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -847,8 +854,8 @@
       <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="J9" s="3">
+        <v>100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -868,20 +875,20 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>1900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
-        <v>0</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
+      <c r="U9" s="3">
+        <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
@@ -892,31 +899,34 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>400</v>
+      </c>
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
-        <v>300</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>200</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -936,20 +946,20 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>-1900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-100</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
+      <c r="U10" s="3">
+        <v>0</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,59 +999,60 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E12" s="3">
         <v>14400</v>
       </c>
-      <c r="E12" s="3">
-        <v>12000</v>
-      </c>
       <c r="F12" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G12" s="3">
         <v>16100</v>
       </c>
-      <c r="G12" s="3">
-        <v>15000</v>
-      </c>
       <c r="H12" s="3">
-        <v>15300</v>
+        <v>16600</v>
       </c>
       <c r="I12" s="3">
-        <v>17500</v>
+        <v>15800</v>
       </c>
       <c r="J12" s="3">
         <v>18200</v>
       </c>
       <c r="K12" s="3">
+        <v>18200</v>
+      </c>
+      <c r="L12" s="3">
         <v>16700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27600</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,35 +1139,38 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>400</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>2300</v>
+        <v>-3400</v>
       </c>
       <c r="H14" s="3">
-        <v>1100</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J14" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K14" s="3">
         <v>9500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,12 +1189,12 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,31 +1210,34 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,64 +1307,65 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E17" s="3">
         <v>27100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23800</v>
       </c>
-      <c r="F17" s="3">
-        <v>28300</v>
-      </c>
       <c r="G17" s="3">
+        <v>27900</v>
+      </c>
+      <c r="H17" s="3">
         <v>27400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1349,32 +1376,35 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-26500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-23300</v>
-      </c>
       <c r="F18" s="3">
-        <v>-27900</v>
+        <v>-23400</v>
       </c>
       <c r="G18" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="H18" s="3">
         <v>-27200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-26900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29200</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1390,23 +1420,23 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-32200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-36700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
+      <c r="U18" s="3">
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,31 +1476,32 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3400</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>3800</v>
+        <v>-500</v>
       </c>
       <c r="F20" s="3">
-        <v>5800</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="3">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-400</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1484,23 +1518,23 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1511,31 +1545,34 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-21700</v>
+        <v>-26800</v>
       </c>
       <c r="E21" s="3">
-        <v>-18400</v>
+        <v>-24600</v>
       </c>
       <c r="F21" s="3">
-        <v>-21000</v>
+        <v>-22000</v>
       </c>
       <c r="G21" s="3">
-        <v>-23600</v>
+        <v>-26500</v>
       </c>
       <c r="H21" s="3">
-        <v>-24500</v>
+        <v>-26200</v>
       </c>
       <c r="I21" s="3">
-        <v>-22800</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-25800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-28000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1552,18 +1589,18 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-35500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-35700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1602,8 +1642,8 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1611,11 +1651,11 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1624,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>1000</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1638,8 +1678,8 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1647,64 +1687,67 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-33100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-29400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-36600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1715,31 +1758,34 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,64 +1900,67 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-22000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-32400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-29400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-11800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-36600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1919,64 +1971,67 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-32400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-29400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,31 +2326,34 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3400</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>-3800</v>
+        <v>500</v>
       </c>
       <c r="F32" s="3">
-        <v>-5800</v>
+        <v>300</v>
       </c>
       <c r="G32" s="3">
-        <v>-2500</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1300</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>400</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -2300,23 +2370,23 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2327,64 +2397,67 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-32400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-29400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-36600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,64 +2539,67 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-32400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-29400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-36600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2531,70 +2610,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2686,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,64 +2742,65 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E41" s="3">
         <v>59600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>53200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>133900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>93800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>87900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>81700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>81300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>35000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>35800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>62100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>521900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>37900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1200</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2724,58 +2811,61 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>154100</v>
+      </c>
+      <c r="E42" s="3">
         <v>158600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>182300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>123900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>180800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>209300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>240400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>267000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>293800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>319400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>399800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>435500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>438100</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
@@ -2783,8 +2873,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2792,32 +2882,35 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,8 +2926,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2860,32 +2953,35 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="E44" s="3">
         <v>4900</v>
       </c>
       <c r="F44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G44" s="3">
         <v>3900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1700</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2901,8 +2997,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2928,65 +3024,68 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>7400</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>7300</v>
+        <v>200</v>
       </c>
       <c r="I45" s="3">
-        <v>6100</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>6900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,65 +3095,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>205800</v>
+      </c>
+      <c r="E46" s="3">
         <v>226500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>244400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>266300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>284800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>306800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>330000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>358200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>378900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>405100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>439800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>477200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>505200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>524100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>37900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,31 +3166,34 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3105,11 +3210,11 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>115000</v>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>115000</v>
@@ -3117,8 +3222,8 @@
       <c r="S47" s="3">
         <v>115000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>115000</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3132,67 +3237,70 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E48" s="3">
         <v>29500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3">
         <v>2000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3200,34 +3308,37 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>100</v>
-      </c>
-      <c r="E49" s="3">
-        <v>500</v>
       </c>
       <c r="F49" s="3">
         <v>500</v>
       </c>
       <c r="G49" s="3">
+        <v>500</v>
+      </c>
+      <c r="H49" s="3">
         <v>600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>9500</v>
@@ -3238,8 +3349,8 @@
       <c r="N49" s="3">
         <v>9500</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>9500</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -3247,17 +3358,17 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,8 +3521,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3443,28 +3563,28 @@
         <v>700</v>
       </c>
       <c r="O52" s="3">
+        <v>700</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,65 +3663,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>236500</v>
+      </c>
+      <c r="E54" s="3">
         <v>256700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>275600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>298300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>318100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>341200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>365000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>391500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>418000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>443300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>476100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>503200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>509500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>527000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>115800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>116300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,61 +3790,62 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3728,31 +3859,34 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3778,14 +3912,14 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -3796,65 +3930,68 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9600</v>
+        <v>1500</v>
       </c>
       <c r="E59" s="3">
-        <v>6800</v>
+        <v>1500</v>
       </c>
       <c r="F59" s="3">
+        <v>500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>10900</v>
+      </c>
+      <c r="M59" s="3">
+        <v>9100</v>
+      </c>
+      <c r="N59" s="3">
         <v>9800</v>
       </c>
-      <c r="G59" s="3">
-        <v>9000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>9400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>11800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>10900</v>
-      </c>
-      <c r="L59" s="3">
-        <v>9100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>9800</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
       <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,64 +4001,67 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E60" s="3">
         <v>11000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2800</v>
-      </c>
-      <c r="S60" s="3">
-        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3">
+        <v>100</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -3932,31 +4072,34 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>14700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4000,62 +4143,65 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12500</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>13800</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="3">
-        <v>15000</v>
+        <v>1300</v>
       </c>
       <c r="H62" s="3">
-        <v>15700</v>
+        <v>1100</v>
       </c>
       <c r="I62" s="3">
-        <v>15900</v>
+        <v>900</v>
       </c>
       <c r="J62" s="3">
+        <v>600</v>
+      </c>
+      <c r="K62" s="3">
         <v>17100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,65 +4427,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E66" s="3">
         <v>23500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4550,11 +4718,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>195800</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,64 +4809,67 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-563500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-538200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-515100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-495600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-473600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-448900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-423300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-399700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-366500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-334800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-302400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-267200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-237800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-219700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-172200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,64 +5093,67 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>210500</v>
+      </c>
+      <c r="E76" s="3">
         <v>233300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>253800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>271600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>292100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>315300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>339000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>358700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>387500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>413500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>441900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>477000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>493900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>503900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-159700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>112200</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5235,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,64 +5311,67 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-32400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-29400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-36600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,67 +5411,68 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
       </c>
       <c r="F83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>500</v>
+      </c>
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="J83" s="3">
-        <v>800</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,59 +5835,62 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-23200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,58 +5935,59 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="E91" s="3">
         <v>-1100</v>
       </c>
       <c r="F91" s="3">
-        <v>-400</v>
+        <v>-1000</v>
       </c>
       <c r="G91" s="3">
-        <v>-1400</v>
+        <v>400</v>
       </c>
       <c r="H91" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="I91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="J91" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-500</v>
       </c>
       <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>-500</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5774,8 +5995,8 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,58 +6146,61 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E94" s="3">
         <v>24800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>61100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>27100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>29200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>26000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>25500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>17200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>72800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>21700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-439900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-500</v>
       </c>
       <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>-500</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5978,8 +6208,8 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,31 +6246,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,59 +6528,62 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
       </c>
       <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>515200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>116300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,16 +6599,19 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -6382,8 +6631,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6421,59 +6670,62 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E102" s="3">
         <v>6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-80700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>46300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-459800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>485500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,101 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,35 +760,38 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>200</v>
       </c>
       <c r="I8" s="3">
         <v>200</v>
       </c>
       <c r="J8" s="3">
+        <v>200</v>
+      </c>
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -804,8 +807,8 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -831,25 +834,28 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>300</v>
-      </c>
-      <c r="F9" s="3">
-        <v>200</v>
       </c>
       <c r="G9" s="3">
         <v>200</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
@@ -857,8 +863,8 @@
       <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
+      <c r="K9" s="3">
+        <v>100</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
@@ -878,20 +884,20 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3">
         <v>1900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
+      <c r="V9" s="3">
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
@@ -902,25 +908,28 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E10" s="3">
         <v>400</v>
       </c>
       <c r="F10" s="3">
+        <v>400</v>
+      </c>
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
@@ -928,8 +937,8 @@
       <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>100</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
@@ -949,20 +958,20 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3">
         <v>-1900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-100</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
+      <c r="V10" s="3">
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
@@ -973,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,62 +1012,63 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E12" s="3">
         <v>16200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12100</v>
       </c>
-      <c r="G12" s="3">
-        <v>16100</v>
-      </c>
       <c r="H12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I12" s="3">
         <v>16600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15800</v>
-      </c>
-      <c r="J12" s="3">
-        <v>18200</v>
       </c>
       <c r="K12" s="3">
         <v>18200</v>
       </c>
       <c r="L12" s="3">
+        <v>18200</v>
+      </c>
+      <c r="M12" s="3">
         <v>16700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27600</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,13 +1158,16 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1156,24 +1175,24 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3400</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,12 +1211,12 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,35 +1232,38 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I15" s="3">
         <v>1200</v>
       </c>
-      <c r="H15" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1284,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,67 +1333,68 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E17" s="3">
         <v>28900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23800</v>
       </c>
-      <c r="G17" s="3">
-        <v>27900</v>
-      </c>
       <c r="H17" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I17" s="3">
         <v>27400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>100</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
@@ -1379,35 +1405,38 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-28100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-27500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-27200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-29200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1423,23 +1452,23 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-32200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-36700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
+      <c r="V18" s="3">
+        <v>0</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
@@ -1450,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,35 +1509,36 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
       </c>
       <c r="H20" s="3">
         <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1521,23 +1554,23 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-3500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1548,35 +1581,38 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-26800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-24600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-26500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-26200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-28000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1592,18 +1628,18 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-35500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-35700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1655,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1645,8 +1684,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1654,11 +1693,11 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1667,13 +1706,13 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>1000</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1681,8 +1720,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1690,67 +1729,70 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-33100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-32400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-29400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-35700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
@@ -1761,16 +1803,19 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1787,8 +1832,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1832,8 +1877,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,67 +1951,70 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-32400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-29400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-35700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-36600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
@@ -1974,67 +2025,70 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-32400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-29400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-35700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
@@ -2045,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,35 +2395,38 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
       </c>
       <c r="H32" s="3">
         <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,23 +2442,23 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>3500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2400,67 +2469,70 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-29400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-35700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,67 +2617,70 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-29400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-35700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
@@ -2613,73 +2691,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,67 +2828,68 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E41" s="3">
         <v>42300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>59600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>53200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>133900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>93800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>87900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>81700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>81300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>35000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>62100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>521900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>37900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1200</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
+      <c r="V41" s="3">
+        <v>0</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
@@ -2814,61 +2900,64 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E42" s="3">
         <v>154100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>158600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>182300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>123900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>180800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>209300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>240400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>267000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>293800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>319400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>399800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>435500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>438100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
@@ -2876,8 +2965,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -2885,35 +2974,38 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,8 +3021,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2956,8 +3048,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2965,26 +3060,26 @@
         <v>4100</v>
       </c>
       <c r="E44" s="3">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="F44" s="3">
         <v>4900</v>
       </c>
       <c r="G44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H44" s="3">
         <v>3900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1700</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3000,8 +3095,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3027,8 +3122,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3044,51 +3142,51 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
-        <v>200</v>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I45" s="3">
         <v>200</v>
       </c>
       <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,68 +3196,71 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E46" s="3">
         <v>205800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>226500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>244400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>266300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>284800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>306800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>330000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>358200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>378900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>405100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>439800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>477200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>505200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>524100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>37900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>100</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3270,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3195,8 +3299,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3213,11 +3317,11 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
-        <v>115000</v>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>115000</v>
@@ -3225,8 +3329,8 @@
       <c r="T47" s="3">
         <v>115000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>115000</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3240,70 +3344,73 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E48" s="3">
         <v>29900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3">
         <v>2000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3311,8 +3418,11 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3320,28 +3430,28 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>100</v>
-      </c>
-      <c r="F49" s="3">
-        <v>500</v>
       </c>
       <c r="G49" s="3">
         <v>500</v>
       </c>
       <c r="H49" s="3">
+        <v>500</v>
+      </c>
+      <c r="I49" s="3">
         <v>600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>900</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="M49" s="3">
         <v>9500</v>
@@ -3352,8 +3462,8 @@
       <c r="O49" s="3">
         <v>9500</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>9500</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -3361,17 +3471,17 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3382,8 +3492,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,13 +3640,16 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>700</v>
@@ -3566,28 +3685,28 @@
         <v>700</v>
       </c>
       <c r="P52" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -3595,8 +3714,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,68 +3788,71 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>247900</v>
+      </c>
+      <c r="E54" s="3">
         <v>236500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>256700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>275600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>298300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>318100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>341200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>365000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>391500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>418000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>443300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>476100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>503200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>509500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>527000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>115800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>40600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>116300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,64 +3920,65 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3862,35 +3992,38 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1600</v>
       </c>
       <c r="G58" s="3">
         <v>1600</v>
       </c>
       <c r="H58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I58" s="3">
         <v>1500</v>
       </c>
       <c r="J58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3915,14 +4048,14 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -3933,68 +4066,71 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E59" s="3">
         <v>1500</v>
       </c>
       <c r="F59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
       </c>
       <c r="J59" s="3">
         <v>400</v>
       </c>
       <c r="K59" s="3">
+        <v>400</v>
+      </c>
+      <c r="L59" s="3">
         <v>11800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
       <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,67 +4140,70 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E60" s="3">
         <v>15300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2800</v>
-      </c>
-      <c r="T60" s="3">
-        <v>100</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
+      <c r="V60" s="3">
+        <v>100</v>
       </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
@@ -4075,35 +4214,38 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E61" s="3">
         <v>10200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4146,65 +4288,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,68 +4584,71 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E66" s="3">
         <v>25900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4721,11 +4888,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>195800</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,67 +4982,70 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-596600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-563500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-538200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-515100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-495600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-473600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-448900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-423300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-399700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-366500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-334800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-302400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-267200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-237800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-219700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-14000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-172200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -4883,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,67 +5278,70 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>215400</v>
+      </c>
+      <c r="E76" s="3">
         <v>210500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>233300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>253800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>271600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>292100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>315300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>339000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>358700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>387500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>413500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>441900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>477000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>493900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>503900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>97100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-159700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>112200</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -5167,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,73 +5426,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,67 +5505,70 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-29400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-35700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
@@ -5385,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,70 +5609,71 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>800</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
       </c>
       <c r="H83" s="3">
+        <v>800</v>
+      </c>
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5483,8 +5681,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,62 +6051,65 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-23200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-23200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-29400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,61 +6155,62 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-500</v>
       </c>
       <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>-500</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5998,8 +6218,8 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6007,8 +6227,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,61 +6375,64 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E94" s="3">
         <v>5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>61100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>27100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>29200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>26000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>25500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>17200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>72800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>21700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-439900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-700</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-500</v>
       </c>
       <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>-500</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -6211,8 +6440,8 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6220,8 +6449,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6273,8 +6506,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6318,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,62 +6773,65 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>35800</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
       </c>
       <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>515200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>116300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,8 +6847,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6634,8 +6882,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6673,62 +6921,65 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-80700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>46300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-26300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-459800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>485500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,104 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,38 +764,41 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>400</v>
-      </c>
-      <c r="I8" s="3">
-        <v>200</v>
       </c>
       <c r="J8" s="3">
         <v>200</v>
       </c>
       <c r="K8" s="3">
+        <v>200</v>
+      </c>
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,8 +814,8 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -837,28 +841,31 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>200</v>
       </c>
       <c r="H9" s="3">
         <v>200</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J9" s="3">
         <v>100</v>
@@ -866,8 +873,8 @@
       <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
+      <c r="L9" s="3">
+        <v>100</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
@@ -887,20 +894,20 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3">
         <v>1900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
+      <c r="W9" s="3">
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
@@ -911,28 +918,31 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
-      </c>
-      <c r="E10" s="3">
-        <v>400</v>
       </c>
       <c r="F10" s="3">
         <v>400</v>
       </c>
       <c r="G10" s="3">
+        <v>400</v>
+      </c>
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
@@ -940,8 +950,8 @@
       <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="L10" s="3">
+        <v>100</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -961,20 +971,20 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3">
         <v>-1900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-100</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
+      <c r="W10" s="3">
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
@@ -985,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,65 +1026,66 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E12" s="3">
         <v>17100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15800</v>
-      </c>
-      <c r="K12" s="3">
-        <v>18200</v>
       </c>
       <c r="L12" s="3">
         <v>18200</v>
       </c>
       <c r="M12" s="3">
+        <v>18200</v>
+      </c>
+      <c r="N12" s="3">
         <v>16700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>27600</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,41 +1178,44 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1214,12 +1234,12 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1235,38 +1255,41 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1100</v>
       </c>
       <c r="H15" s="3">
         <v>1100</v>
       </c>
       <c r="I15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1309,8 +1332,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,70 +1360,71 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E17" s="3">
         <v>32000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>26000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1408,38 +1435,41 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-28100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-29200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1455,23 +1485,23 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-32200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-36700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
+      <c r="W18" s="3">
+        <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
@@ -1482,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,38 +1543,39 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
       </c>
       <c r="I20" s="3">
         <v>200</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1557,23 +1591,23 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>-3500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1584,38 +1618,41 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-34500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-26800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-24600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-24700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1631,18 +1668,18 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-35500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-35700</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,8 +1695,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1687,8 +1727,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1696,11 +1736,11 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1709,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>1000</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1723,8 +1763,8 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1732,70 +1772,73 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-33100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-22000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-33100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-32400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-35200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-35700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-36600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1806,8 +1849,11 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1817,8 +1863,8 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1835,8 +1881,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1880,8 +1926,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,70 +2003,73 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-33100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-22000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-32400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-35200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-35700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-36600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -2028,70 +2080,73 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-22000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-32400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-35200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-35700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2102,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,38 +2465,41 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
       </c>
       <c r="I32" s="3">
         <v>-200</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2445,23 +2515,23 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>3500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2472,70 +2542,73 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-33100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-22000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-24700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-32400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-35200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-35700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-36600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2546,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,70 +2696,73 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-33100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-22000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-24700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-32400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-35200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-35700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-36600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2694,76 +2773,79 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,70 +2915,71 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E41" s="3">
         <v>49200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>59600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>53200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>133900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>93800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>87900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>81700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>84300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>78300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>81300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>62100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>521900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1200</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+      <c r="W41" s="3">
+        <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -2903,64 +2990,67 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>195300</v>
+      </c>
+      <c r="E42" s="3">
         <v>160400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>154100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>158600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>182300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>123900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>180800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>209300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>240400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>267000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>293800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>319400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>399800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>435500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>438100</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
@@ -2968,8 +3058,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -2977,38 +3067,41 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,8 +3117,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3051,38 +3144,41 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="E44" s="3">
         <v>4100</v>
       </c>
       <c r="F44" s="3">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="G44" s="3">
         <v>4900</v>
       </c>
       <c r="H44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I44" s="3">
         <v>3900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,8 +3194,8 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3125,8 +3221,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3145,51 +3244,51 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
-        <v>200</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
       </c>
       <c r="K45" s="3">
+        <v>200</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,71 +3298,74 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>241800</v>
+      </c>
+      <c r="E46" s="3">
         <v>218000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>205800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>226500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>244400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>266300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>284800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>306800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>330000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>358200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>378900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>405100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>439800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>477200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>505200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>524100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3302,8 +3407,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3320,11 +3425,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
-        <v>115000</v>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>115000</v>
@@ -3332,8 +3437,8 @@
       <c r="U47" s="3">
         <v>115000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>115000</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3347,73 +3452,76 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E48" s="3">
         <v>29100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3">
         <v>2000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3421,8 +3529,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3433,28 +3544,28 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>500</v>
       </c>
       <c r="H49" s="3">
         <v>500</v>
       </c>
       <c r="I49" s="3">
+        <v>500</v>
+      </c>
+      <c r="J49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>9500</v>
@@ -3465,8 +3576,8 @@
       <c r="P49" s="3">
         <v>9500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>9500</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3474,17 +3585,17 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3495,8 +3606,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,8 +3760,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3652,7 +3772,7 @@
         <v>800</v>
       </c>
       <c r="E52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F52" s="3">
         <v>700</v>
@@ -3688,28 +3808,28 @@
         <v>700</v>
       </c>
       <c r="Q52" s="3">
+        <v>700</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,71 +3914,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>271200</v>
+      </c>
+      <c r="E54" s="3">
         <v>247900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>236500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>256700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>275600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>298300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>318100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>341200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>365000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>391500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>418000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>443300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>476100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>503200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>509500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>527000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>115800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>40600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>116300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,8 +4051,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3930,58 +4061,58 @@
         <v>1900</v>
       </c>
       <c r="E57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -3995,38 +4126,41 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1600</v>
       </c>
       <c r="H58" s="3">
         <v>1600</v>
       </c>
       <c r="I58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="J58" s="3">
         <v>1500</v>
       </c>
       <c r="K58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4051,14 +4185,14 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4069,71 +4203,74 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2500</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1500</v>
       </c>
       <c r="F59" s="3">
         <v>1500</v>
       </c>
       <c r="G59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
       </c>
       <c r="K59" s="3">
         <v>400</v>
       </c>
       <c r="L59" s="3">
+        <v>400</v>
+      </c>
+      <c r="M59" s="3">
         <v>11800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
       <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,70 +4280,73 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E60" s="3">
         <v>18200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
-      </c>
-      <c r="U60" s="3">
-        <v>100</v>
       </c>
       <c r="V60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
+      <c r="W60" s="3">
+        <v>100</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
@@ -4217,38 +4357,41 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E61" s="3">
         <v>9300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4291,68 +4434,71 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E62" s="3">
         <v>5000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4000</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4365,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,71 +4742,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E66" s="3">
         <v>32500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4891,11 +5059,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>195800</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,70 +5156,73 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-615800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-596600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-563500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-538200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-515100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-495600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-473600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-448900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-423300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-399700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-366500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-334800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-302400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-267200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-237800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-219700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-14000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-172200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-100</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,70 +5464,73 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>246900</v>
+      </c>
+      <c r="E76" s="3">
         <v>215400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>210500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>233300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>253800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>271600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>292100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>315300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>339000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>358700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>387500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>413500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>441900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>477000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>493900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>503900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>97100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-159700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>112200</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,76 +5618,79 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,70 +5700,73 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-33100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-22000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-24700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-32400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-35200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-35700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-36600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5582,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,8 +5808,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5619,64 +5818,64 @@
         <v>1100</v>
       </c>
       <c r="E83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
       </c>
       <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>300</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5684,8 +5883,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,65 +6268,68 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-23200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-23200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-19200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6128,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,64 +6376,65 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-500</v>
       </c>
       <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>-500</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -6221,8 +6442,8 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6230,8 +6451,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,64 +6605,67 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>61100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>27100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>29200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>26000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>25500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>17200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>72800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>21700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-439900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-500</v>
       </c>
       <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>-500</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6443,8 +6673,8 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6452,8 +6682,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6743,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,65 +7019,68 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E100" s="3">
         <v>35800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>515200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>116300</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,13 +7096,16 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -6885,8 +7134,8 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -6924,65 +7173,68 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E102" s="3">
         <v>7000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-80700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>46300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-459800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>485500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,41 +768,44 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>200</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
       </c>
       <c r="L8" s="3">
+        <v>200</v>
+      </c>
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -817,8 +821,8 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -844,31 +848,34 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>300</v>
-      </c>
-      <c r="H9" s="3">
-        <v>200</v>
       </c>
       <c r="I9" s="3">
         <v>200</v>
       </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -876,8 +883,8 @@
       <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
+      <c r="M9" s="3">
+        <v>100</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
@@ -897,20 +904,20 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3">
         <v>1900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
+      <c r="X9" s="3">
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
@@ -921,31 +928,34 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>400</v>
       </c>
       <c r="G10" s="3">
         <v>400</v>
       </c>
       <c r="H10" s="3">
+        <v>400</v>
+      </c>
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -953,8 +963,8 @@
       <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>100</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
@@ -974,20 +984,20 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3">
         <v>-1900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-100</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
+      <c r="X10" s="3">
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,68 +1040,69 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E12" s="3">
         <v>13700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>18200</v>
       </c>
       <c r="M12" s="3">
         <v>18200</v>
       </c>
       <c r="N12" s="3">
+        <v>18200</v>
+      </c>
+      <c r="O12" s="3">
         <v>16700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27600</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,44 +1198,47 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1237,12 +1257,12 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,41 +1278,44 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1100</v>
       </c>
       <c r="I15" s="3">
         <v>1100</v>
       </c>
       <c r="J15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,73 +1387,74 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E17" s="3">
         <v>26000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>30200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>36700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1438,41 +1465,44 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-30800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-28100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-26500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-23400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-25600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-27200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-26900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-29200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1488,23 +1518,23 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-32200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-36700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
+      <c r="X18" s="3">
+        <v>0</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,41 +1577,42 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1594,23 +1628,23 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>-3500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1621,41 +1655,44 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-34500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-24600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-22000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1671,18 +1708,18 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-35500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-35700</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1735,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1730,8 +1770,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1739,11 +1779,11 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1752,13 +1792,13 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>1000</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1766,8 +1806,8 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1775,73 +1815,76 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-33100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-32400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-29400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-35700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-36600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1852,8 +1895,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1866,8 +1912,8 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1884,8 +1930,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,73 +2055,76 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-33100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-22000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-23600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-33100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-32400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-29400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-35700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-36600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2083,73 +2135,76 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-33100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-23600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-33100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-29400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-35700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-36600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,41 +2535,44 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2518,23 +2588,23 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>3500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2545,73 +2615,76 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-33100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-22000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-23600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-33100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-29400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-35700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-36600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,73 +2775,76 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-33100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-22000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-23600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-33100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-29400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-35700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-36600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2776,79 +2855,82 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,73 +3002,74 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E41" s="3">
         <v>37300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>53200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>133900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>93800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>87900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>81700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>84300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>78300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>81300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>62100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>521900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1200</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
+      <c r="X41" s="3">
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
@@ -2993,67 +3080,70 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E42" s="3">
         <v>195300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>160400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>154100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>158600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>182300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>123900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>180800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>209300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>240400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>267000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>293800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>319400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>399800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>435500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>438100</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
@@ -3061,8 +3151,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3070,41 +3160,44 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3120,8 +3213,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3147,41 +3240,44 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E44" s="3">
         <v>4400</v>
-      </c>
-      <c r="E44" s="3">
-        <v>4100</v>
       </c>
       <c r="F44" s="3">
         <v>4100</v>
       </c>
       <c r="G44" s="3">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="H44" s="3">
         <v>4900</v>
       </c>
       <c r="I44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J44" s="3">
         <v>3900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1700</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,8 +3293,8 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3224,8 +3320,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3247,51 +3346,51 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
-        <v>200</v>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,74 +3400,77 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>226500</v>
+      </c>
+      <c r="E46" s="3">
         <v>241800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>218000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>205800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>226500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>244400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>266300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>284800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>306800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>330000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>358200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>378900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>405100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>439800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>477200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>505200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>524100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>37900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3410,8 +3515,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3428,11 +3533,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3">
-        <v>115000</v>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>115000</v>
@@ -3440,8 +3545,8 @@
       <c r="V47" s="3">
         <v>115000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>115000</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3455,76 +3560,79 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E48" s="3">
         <v>28600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
         <v>2000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -3532,8 +3640,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3547,28 +3658,28 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>100</v>
-      </c>
-      <c r="H49" s="3">
-        <v>500</v>
       </c>
       <c r="I49" s="3">
         <v>500</v>
       </c>
       <c r="J49" s="3">
+        <v>500</v>
+      </c>
+      <c r="K49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>9500</v>
@@ -3579,8 +3690,8 @@
       <c r="Q49" s="3">
         <v>9500</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>9500</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3588,17 +3699,17 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,8 +3880,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3775,7 +3895,7 @@
         <v>800</v>
       </c>
       <c r="F52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G52" s="3">
         <v>700</v>
@@ -3811,28 +3931,28 @@
         <v>700</v>
       </c>
       <c r="R52" s="3">
+        <v>700</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
         <v>700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,74 +4040,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>254400</v>
+      </c>
+      <c r="E54" s="3">
         <v>271200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>247900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>236500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>256700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>275600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>298300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>318100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>341200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>365000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>391500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>418000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>443300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>476100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>503200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>509500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>527000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>115800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>40600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>116300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>100</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,70 +4182,71 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1900</v>
+        <v>2200</v>
       </c>
       <c r="E57" s="3">
         <v>1900</v>
       </c>
       <c r="F57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4129,41 +4260,44 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1600</v>
       </c>
       <c r="I58" s="3">
         <v>1600</v>
       </c>
       <c r="J58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="K58" s="3">
         <v>1500</v>
       </c>
       <c r="L58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4188,14 +4322,14 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4206,74 +4340,77 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2000</v>
+        <v>11200</v>
       </c>
       <c r="E59" s="3">
+        <v>700</v>
+      </c>
+      <c r="F59" s="3">
         <v>2500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1500</v>
       </c>
       <c r="G59" s="3">
         <v>1500</v>
       </c>
       <c r="H59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
-      </c>
-      <c r="K59" s="3">
-        <v>400</v>
       </c>
       <c r="L59" s="3">
         <v>400</v>
       </c>
       <c r="M59" s="3">
+        <v>400</v>
+      </c>
+      <c r="N59" s="3">
         <v>11800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
         <v>1400</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,73 +4420,76 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2800</v>
-      </c>
-      <c r="V60" s="3">
-        <v>100</v>
       </c>
       <c r="W60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
+      <c r="X60" s="3">
+        <v>100</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
@@ -4360,41 +4500,44 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E61" s="3">
         <v>10100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4437,71 +4580,74 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>17100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,74 +4900,77 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E66" s="3">
         <v>24300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>34300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5062,11 +5230,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>195800</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,73 +5330,76 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-644700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-615800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-596600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-563500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-538200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-515100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-495600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-473600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-448900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-423300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-399700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-366500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-334800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-302400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-267200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-237800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-219700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-172200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,73 +5650,76 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E76" s="3">
         <v>246900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>215400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>210500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>233300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>253800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>271600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>292100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>315300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>339000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>358700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>387500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>413500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>441900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>477000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>493900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>503900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>97100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-159700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>112200</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
+      <c r="X76" s="3">
+        <v>0</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,79 +5810,82 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,73 +5895,76 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-33100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-22000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-23600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-33100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-29400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-35700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-36600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,76 +6007,77 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
       </c>
       <c r="F83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>800</v>
       </c>
       <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>900</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -5886,8 +6085,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,68 +6485,71 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-26200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-29400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,67 +6597,68 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-500</v>
       </c>
       <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>-500</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6445,8 +6666,8 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6454,8 +6675,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,67 +6835,70 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-34200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>24800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>61100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>27100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>29200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>26000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>25500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>17200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>72800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>21700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-439900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-500</v>
       </c>
       <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>-500</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6676,8 +6906,8 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6746,8 +6980,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,68 +7265,71 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>48400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>35800</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>515200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>116300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,16 +7345,19 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -7137,8 +7386,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7176,68 +7425,71 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-80700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>46300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-459800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>485500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,116 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -775,47 +775,50 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E8" s="3">
         <v>600</v>
       </c>
       <c r="F8" s="3">
+        <v>600</v>
+      </c>
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>200</v>
       </c>
       <c r="M8" s="3">
         <v>200</v>
       </c>
       <c r="N8" s="3">
+        <v>200</v>
+      </c>
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,8 +834,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -858,37 +861,40 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>200</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M9" s="3">
         <v>100</v>
@@ -896,8 +902,8 @@
       <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
+      <c r="O9" s="3">
+        <v>100</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
@@ -917,20 +923,20 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3">
         <v>1900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>100</v>
       </c>
-      <c r="Y9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
+      <c r="Z9" s="3">
+        <v>0</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
@@ -941,37 +947,40 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>400</v>
       </c>
       <c r="I10" s="3">
         <v>400</v>
       </c>
       <c r="J10" s="3">
+        <v>400</v>
+      </c>
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
       </c>
       <c r="M10" s="3">
         <v>100</v>
@@ -979,8 +988,8 @@
       <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>100</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
@@ -1000,20 +1009,20 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3">
         <v>-1900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-100</v>
       </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
+      <c r="Z10" s="3">
+        <v>0</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
@@ -1024,8 +1033,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,74 +1067,75 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E12" s="3">
         <v>13900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13700</v>
       </c>
-      <c r="G12" s="3">
-        <v>17100</v>
-      </c>
       <c r="H12" s="3">
+        <v>17000</v>
+      </c>
+      <c r="I12" s="3">
         <v>16200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15800</v>
-      </c>
-      <c r="N12" s="3">
-        <v>18200</v>
       </c>
       <c r="O12" s="3">
         <v>18200</v>
       </c>
       <c r="P12" s="3">
+        <v>18200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>16700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>27600</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,8 +1151,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,50 +1237,53 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>15400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1283,12 +1302,12 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1304,8 +1323,11 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1316,35 +1338,35 @@
         <v>1200</v>
       </c>
       <c r="F15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1100</v>
       </c>
       <c r="K15" s="3">
         <v>1100</v>
       </c>
       <c r="L15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M15" s="3">
         <v>1200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>800</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1387,8 +1409,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,79 +1440,80 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E17" s="3">
         <v>24900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26000</v>
       </c>
-      <c r="G17" s="3">
-        <v>32000</v>
-      </c>
       <c r="H17" s="3">
+        <v>31900</v>
+      </c>
+      <c r="I17" s="3">
         <v>28900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>30200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>36700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>100</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
+      <c r="Z17" s="3">
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
@@ -1498,47 +1524,50 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-30800</v>
-      </c>
       <c r="H18" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-28100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-25600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-27200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-29200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1554,23 +1583,23 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-32200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-36700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
+      <c r="Z18" s="3">
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
@@ -1581,8 +1610,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,47 +1644,48 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,23 +1701,23 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1695,47 +1728,50 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-26600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-34500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-26800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-22000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-25800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-28000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1751,18 +1787,18 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-35500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-35700</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1778,8 +1814,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1816,8 +1855,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1825,11 +1864,11 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1838,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1852,8 +1891,8 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1861,79 +1900,82 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-33100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-32400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-35200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-29400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-35700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-36600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
+      <c r="Z23" s="3">
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
@@ -1944,8 +1986,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1964,8 +2009,8 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1982,8 +2027,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2027,8 +2072,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,79 +2158,82 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-22000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-32400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-35200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-29400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-35700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-36600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
+      <c r="Z26" s="3">
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
@@ -2193,79 +2244,82 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-22000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-23600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-33100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-32400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-35200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-29400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-35700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-36600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
+      <c r="Z27" s="3">
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
@@ -2276,8 +2330,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2416,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2502,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2588,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,47 +2674,50 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2664,23 +2733,23 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>3500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2691,79 +2760,82 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-22000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-23600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-33100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-32400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-35200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-29400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-35700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-36600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
+      <c r="Z33" s="3">
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
@@ -2774,8 +2846,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,79 +2932,82 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-22000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-23600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-33100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-32400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-35200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-29400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-35700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-36600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
+      <c r="Z35" s="3">
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
@@ -2940,85 +3018,88 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3109,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3143,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,79 +3175,80 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E41" s="3">
         <v>30900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>53200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>93800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>87900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>81700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>78300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>81300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>35000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>62100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>521900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1200</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
+      <c r="Z41" s="3">
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
@@ -3173,73 +3259,76 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>141300</v>
+      </c>
+      <c r="E42" s="3">
         <v>194900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>192000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>195300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>160400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>154100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>158600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>182300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>123900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>180800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>209300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>240400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>267000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>293800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>319400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>399800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>435500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>438100</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
@@ -3247,8 +3336,8 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3256,47 +3345,50 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E43" s="3">
         <v>5400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
-        <v>1300</v>
-      </c>
       <c r="H43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I43" s="3">
         <v>1000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3312,8 +3404,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3339,47 +3431,50 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E44" s="3">
         <v>3500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4400</v>
-      </c>
-      <c r="G44" s="3">
-        <v>4100</v>
       </c>
       <c r="H44" s="3">
         <v>4100</v>
       </c>
       <c r="I44" s="3">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="J44" s="3">
         <v>4900</v>
       </c>
       <c r="K44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L44" s="3">
         <v>3900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3395,8 +3490,8 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3422,8 +3517,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3451,51 +3549,51 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
-        <v>200</v>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M45" s="3">
         <v>200</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,80 +3603,83 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E46" s="3">
         <v>238000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>226500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>241800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>218000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>205800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>226500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>244400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>266300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>284800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>306800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>330000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>358200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>378900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>405100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>439800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>477200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>505200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>524100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>100</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,17 +3689,20 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E47" s="3">
         <v>4700</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3626,8 +3730,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3644,11 +3748,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3">
-        <v>115000</v>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>115000</v>
@@ -3656,8 +3760,8 @@
       <c r="X47" s="3">
         <v>115000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
+      <c r="Y47" s="3">
+        <v>115000</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
@@ -3671,82 +3775,85 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E48" s="3">
         <v>17200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3">
         <v>2000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -3754,8 +3861,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3775,28 +3885,28 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>100</v>
-      </c>
-      <c r="J49" s="3">
-        <v>500</v>
       </c>
       <c r="K49" s="3">
         <v>500</v>
       </c>
       <c r="L49" s="3">
+        <v>500</v>
+      </c>
+      <c r="M49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>900</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="3">
         <v>9500</v>
@@ -3807,8 +3917,8 @@
       <c r="S49" s="3">
         <v>9500</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>9500</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3816,17 +3926,17 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3837,8 +3947,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4033,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,8 +4119,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4012,7 +4131,7 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>800</v>
@@ -4021,7 +4140,7 @@
         <v>800</v>
       </c>
       <c r="H52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
@@ -4057,28 +4176,28 @@
         <v>700</v>
       </c>
       <c r="T52" s="3">
+        <v>700</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3">
         <v>700</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4086,8 +4205,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,80 +4291,83 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>245600</v>
+      </c>
+      <c r="E54" s="3">
         <v>260100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>254400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>271200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>247900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>236500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>256700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>275600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>298300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>318100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>341200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>365000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>391500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>418000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>443300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>476100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>503200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>509500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>527000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>115800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>40600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>116300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>100</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4377,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4411,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,76 +4443,77 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1900</v>
       </c>
       <c r="G57" s="3">
         <v>1900</v>
       </c>
       <c r="H57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I57" s="3">
         <v>2200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
+      <c r="Y57" s="3">
+        <v>0</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
@@ -4397,8 +4527,11 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4409,35 +4542,35 @@
         <v>1800</v>
       </c>
       <c r="F58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1700</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1600</v>
       </c>
       <c r="K58" s="3">
         <v>1600</v>
       </c>
       <c r="L58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="M58" s="3">
         <v>1500</v>
       </c>
       <c r="N58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O58" s="3">
         <v>1400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4462,14 +4595,14 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
@@ -4480,80 +4613,83 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E59" s="3">
         <v>9700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1500</v>
       </c>
       <c r="I59" s="3">
         <v>1500</v>
       </c>
       <c r="J59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
-      </c>
-      <c r="M59" s="3">
-        <v>400</v>
       </c>
       <c r="N59" s="3">
         <v>400</v>
       </c>
       <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4800</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3">
         <v>1400</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
       <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,79 +4699,82 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>24000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2800</v>
-      </c>
-      <c r="X60" s="3">
-        <v>100</v>
       </c>
       <c r="Y60" s="3">
         <v>100</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
+      <c r="Z60" s="3">
+        <v>100</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
@@ -4646,47 +4785,50 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4729,8 +4871,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4741,65 +4886,65 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +4957,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5043,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5129,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,80 +5215,83 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E66" s="3">
         <v>25000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5301,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5335,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5419,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5505,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5404,11 +5571,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>195800</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5424,8 +5591,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,79 +5677,82 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-698000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-680400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-644700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-615800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-596600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-563500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-538200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-515100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-495600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-473600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-448900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-423300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-399700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-366500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-334800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-302400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-267200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-237800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-219700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-14000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-172200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-100</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
+      <c r="Z72" s="3">
+        <v>0</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
@@ -5590,8 +5763,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5849,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5935,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,79 +6021,82 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E76" s="3">
         <v>235200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>221000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>246900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>215400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>210500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>233300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>253800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>271600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>292100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>315300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>339000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>358700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>387500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>413500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>441900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>477000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>493900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>503900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>97100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-159700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>112200</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
+      <c r="Z76" s="3">
+        <v>0</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
@@ -5922,8 +6107,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,85 +6193,88 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6093,79 +6284,82 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-22000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-23600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-33100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-32400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-35200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-29400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-35700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-36600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
+      <c r="Z81" s="3">
+        <v>0</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
@@ -6176,8 +6370,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,82 +6404,83 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1100</v>
       </c>
       <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>900</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6290,8 +6488,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6574,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6660,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6746,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6832,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,74 +6918,77 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-20200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-26200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-25900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-23200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-19200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-29400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6788,8 +7004,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,73 +7038,74 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-500</v>
       </c>
       <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="X91" s="3">
+        <v>-500</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
@@ -6893,8 +7113,8 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6902,8 +7122,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7208,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,73 +7294,76 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-34200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>24800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>61100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>27100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>29200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>26000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>25500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>17200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>72800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>21700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-439900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-500</v>
       </c>
       <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>-500</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -7142,8 +7371,8 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7151,8 +7380,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7414,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7220,8 +7453,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7265,8 +7498,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7584,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7670,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,74 +7756,77 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>47000</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>48400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>35800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>515200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>116300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7597,8 +7842,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7611,8 +7859,8 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -7641,8 +7889,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7680,74 +7928,77 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E102" s="3">
         <v>8700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-80700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>46300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-26300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-459800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>485500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7761,6 +8012,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
   <si>
     <t>QSI</t>
   </si>
@@ -656,119 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -778,50 +779,53 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
-      </c>
-      <c r="E8" s="3">
-        <v>600</v>
       </c>
       <c r="F8" s="3">
         <v>600</v>
       </c>
       <c r="G8" s="3">
+        <v>600</v>
+      </c>
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
-      </c>
-      <c r="M8" s="3">
-        <v>200</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
       </c>
       <c r="O8" s="3">
+        <v>200</v>
+      </c>
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,8 +841,8 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -864,40 +868,43 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>300</v>
-      </c>
-      <c r="K9" s="3">
-        <v>200</v>
       </c>
       <c r="L9" s="3">
         <v>200</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
@@ -905,8 +912,8 @@
       <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
+      <c r="P9" s="3">
+        <v>100</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
@@ -926,20 +933,20 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3">
         <v>1900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>100</v>
       </c>
-      <c r="Z9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
+      <c r="AA9" s="3">
+        <v>0</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
@@ -950,8 +957,11 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -959,31 +969,31 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>600</v>
-      </c>
-      <c r="I10" s="3">
-        <v>400</v>
       </c>
       <c r="J10" s="3">
         <v>400</v>
       </c>
       <c r="K10" s="3">
+        <v>400</v>
+      </c>
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>100</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
@@ -991,8 +1001,8 @@
       <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
+      <c r="P10" s="3">
+        <v>100</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
@@ -1012,20 +1022,20 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3">
         <v>-1900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-100</v>
       </c>
-      <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
+      <c r="AA10" s="3">
+        <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
@@ -1036,8 +1046,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1068,77 +1081,78 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E12" s="3">
         <v>10900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15800</v>
-      </c>
-      <c r="O12" s="3">
-        <v>18200</v>
       </c>
       <c r="P12" s="3">
         <v>18200</v>
       </c>
       <c r="Q12" s="3">
+        <v>18200</v>
+      </c>
+      <c r="R12" s="3">
         <v>16700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>27600</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1168,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,23 +1257,26 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,24 +1289,24 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1305,12 +1325,12 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1326,8 +1346,11 @@
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1341,35 +1364,35 @@
         <v>1200</v>
       </c>
       <c r="G15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1100</v>
       </c>
       <c r="L15" s="3">
         <v>1100</v>
       </c>
       <c r="M15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N15" s="3">
         <v>1200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>800</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1412,8 +1435,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1441,82 +1467,83 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E17" s="3">
         <v>21500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>29500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>30200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>32200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>36700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>100</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
+      <c r="AA17" s="3">
+        <v>0</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
@@ -1527,50 +1554,53 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-25100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-25600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-26900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-29200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1586,23 +1616,23 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-32200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-36700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
+      <c r="AA18" s="3">
+        <v>0</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
@@ -1613,8 +1643,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,50 +1678,51 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1704,23 +1738,23 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
+      <c r="AA20" s="3">
+        <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
@@ -1731,50 +1765,53 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-19700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-34300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-22000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-25800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1790,18 +1827,18 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-35500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-10600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-35700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,8 +1854,11 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1858,8 +1898,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1867,11 +1907,11 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1880,13 +1920,13 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>1000</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1894,8 +1934,8 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1903,82 +1943,85 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-33100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-32400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-35200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-29400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-18100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-35700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-36600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
+      <c r="AA23" s="3">
+        <v>0</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
@@ -1989,13 +2032,16 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -2012,8 +2058,8 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -2030,8 +2076,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2075,8 +2121,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2161,82 +2210,85 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-22000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-31700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-32400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-35200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-29400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-18100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-35700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-36600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
+      <c r="AA26" s="3">
+        <v>0</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
@@ -2247,82 +2299,85 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-22000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-32400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-35200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-29400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-18100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-35700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-36600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
+      <c r="AA27" s="3">
+        <v>0</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
@@ -2333,8 +2388,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2419,8 +2477,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2505,8 +2566,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2591,8 +2655,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2677,50 +2744,53 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2736,23 +2806,23 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>3500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
+      <c r="AA32" s="3">
+        <v>0</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
@@ -2763,82 +2833,85 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-22000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-32400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-35200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-29400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-18100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-35700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-36600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
+      <c r="AA33" s="3">
+        <v>0</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
@@ -2849,8 +2922,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2935,82 +3011,85 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-22000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-32400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-35200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-29400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-18100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-35700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-36600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
+      <c r="AA35" s="3">
+        <v>0</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
@@ -3021,88 +3100,91 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3112,8 +3194,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3144,8 +3229,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3176,82 +3262,83 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E41" s="3">
         <v>21600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>93800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>87900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>81700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>78300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>81300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>35800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>62100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>521900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1200</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
+      <c r="AA41" s="3">
+        <v>0</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
@@ -3262,76 +3349,79 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E42" s="3">
         <v>141300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>194900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>192000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>195300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>160400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>154100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>158600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>182300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>123900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>180800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>209300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>240400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>267000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>293800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>319400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>399800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>435500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>438100</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
@@ -3339,8 +3429,8 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3348,50 +3438,53 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>5900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3407,8 +3500,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3434,50 +3527,53 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E44" s="3">
         <v>3200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4400</v>
-      </c>
-      <c r="H44" s="3">
-        <v>4100</v>
       </c>
       <c r="I44" s="3">
         <v>4100</v>
       </c>
       <c r="J44" s="3">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="K44" s="3">
         <v>4900</v>
       </c>
       <c r="L44" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M44" s="3">
         <v>3900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1700</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3493,8 +3589,8 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3520,8 +3616,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3552,51 +3651,51 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>200</v>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,83 +3705,86 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E46" s="3">
         <v>175900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>238000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>226500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>241800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>218000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>205800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>226500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>244400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>266300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>284800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>306800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>330000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>358200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>378900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>405100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>439800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>477200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>505200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>524100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>37900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>100</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3692,20 +3794,23 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E47" s="3">
         <v>52900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4700</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,8 +3838,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3751,11 +3856,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W47" s="3">
-        <v>115000</v>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>115000</v>
@@ -3763,8 +3868,8 @@
       <c r="Y47" s="3">
         <v>115000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
+      <c r="Z47" s="3">
+        <v>115000</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
@@ -3778,85 +3883,88 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E48" s="3">
         <v>16700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3">
         <v>2000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3864,8 +3972,11 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3888,28 +3999,28 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>100</v>
-      </c>
-      <c r="K49" s="3">
-        <v>500</v>
       </c>
       <c r="L49" s="3">
         <v>500</v>
       </c>
       <c r="M49" s="3">
+        <v>500</v>
+      </c>
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>900</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="R49" s="3">
         <v>9500</v>
@@ -3920,8 +4031,8 @@
       <c r="T49" s="3">
         <v>9500</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>9500</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3929,17 +4040,17 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -3950,8 +4061,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4036,8 +4150,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4122,8 +4239,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4134,7 +4254,7 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>800</v>
@@ -4143,7 +4263,7 @@
         <v>800</v>
       </c>
       <c r="I52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J52" s="3">
         <v>700</v>
@@ -4179,28 +4299,28 @@
         <v>700</v>
       </c>
       <c r="U52" s="3">
+        <v>700</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3">
         <v>700</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4208,8 +4328,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4294,83 +4417,86 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>213300</v>
+      </c>
+      <c r="E54" s="3">
         <v>245600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>260100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>254400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>271200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>247900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>236500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>256700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>275600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>298300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>318100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>341200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>365000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>391500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>418000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>443300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>476100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>503200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>509500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>527000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>115800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>40600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>116300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>100</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4380,8 +4506,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4412,8 +4541,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4444,79 +4574,80 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1900</v>
       </c>
       <c r="H57" s="3">
         <v>1900</v>
       </c>
       <c r="I57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
+      <c r="Z57" s="3">
+        <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
@@ -4530,8 +4661,11 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4545,35 +4679,35 @@
         <v>1800</v>
       </c>
       <c r="G58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1600</v>
       </c>
       <c r="L58" s="3">
         <v>1600</v>
       </c>
       <c r="M58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="N58" s="3">
         <v>1500</v>
       </c>
       <c r="O58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P58" s="3">
         <v>1400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4598,14 +4732,14 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
@@ -4616,83 +4750,86 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>9200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1500</v>
       </c>
       <c r="J59" s="3">
         <v>1500</v>
       </c>
       <c r="K59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
-      </c>
-      <c r="N59" s="3">
-        <v>400</v>
       </c>
       <c r="O59" s="3">
         <v>400</v>
       </c>
       <c r="P59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>11800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1400</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
       <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,82 +4839,85 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E60" s="3">
         <v>23000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2800</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>100</v>
       </c>
       <c r="Z60" s="3">
         <v>100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
+      <c r="AA60" s="3">
+        <v>100</v>
       </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
@@ -4788,50 +4928,53 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4874,8 +5017,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4889,65 +5035,65 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4960,8 +5106,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5046,8 +5195,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5132,8 +5284,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5218,83 +5373,86 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E66" s="3">
         <v>25400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5304,8 +5462,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,8 +5497,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5422,8 +5584,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5508,8 +5673,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5574,11 +5742,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>195800</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5594,8 +5762,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5680,82 +5851,85 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-719700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-698000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-680400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-644700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-615800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-596600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-563500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-538200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-515100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-495600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-473600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-448900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-423300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-399700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-366500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-334800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-302400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-267200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-237800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-219700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-14000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-172200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-100</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
+      <c r="AA72" s="3">
+        <v>0</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
@@ -5766,8 +5940,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5852,8 +6029,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5938,8 +6118,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6024,82 +6207,85 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E76" s="3">
         <v>220200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>235200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>221000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>246900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>215400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>210500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>233300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>253800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>271600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>292100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>315300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>339000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>358700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>387500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>413500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>441900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>477000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>493900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>503900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>97100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-159700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>112200</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
+      <c r="AA76" s="3">
+        <v>0</v>
       </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
@@ -6110,8 +6296,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6196,88 +6385,91 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6287,82 +6479,85 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-22000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-32400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-35200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-29400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-18100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-35700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-36600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
+      <c r="AA81" s="3">
+        <v>0</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
@@ -6373,8 +6568,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6405,85 +6603,86 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1100</v>
       </c>
       <c r="H83" s="3">
         <v>1100</v>
       </c>
       <c r="I83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>800</v>
       </c>
       <c r="L83" s="3">
         <v>800</v>
       </c>
       <c r="M83" s="3">
+        <v>800</v>
+      </c>
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>300</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
       <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>900</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -6491,8 +6690,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6577,8 +6779,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6663,8 +6868,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6749,8 +6957,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6835,8 +7046,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6921,77 +7135,80 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-26200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-23200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-19200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-29400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7007,8 +7224,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7039,76 +7259,77 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-500</v>
       </c>
       <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>-500</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -7116,8 +7337,8 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7125,8 +7346,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7211,8 +7435,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7297,76 +7524,79 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E94" s="3">
         <v>7000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-34200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>61100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>27100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>29200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>26000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>25500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>17200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>72800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>21700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-439900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-500</v>
       </c>
       <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>-500</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -7374,8 +7604,8 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7383,8 +7613,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7415,8 +7648,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7456,8 +7690,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7501,8 +7735,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7587,8 +7824,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7673,8 +7913,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7759,77 +8002,80 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>47000</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>48400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>35800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>515200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>116300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7845,8 +8091,11 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7862,8 +8111,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -7892,8 +8141,8 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -7931,77 +8180,80 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-80700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>46300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-26300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-459800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>485500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8015,6 +8267,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
